--- a/todoMobile.xlsx
+++ b/todoMobile.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anah\bossy\S5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITU\semestre5\cloud\MobileCrypto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8319F5AB-D21A-46CB-9A56-A60477098A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B3CED8-8005-46DC-8DF0-708830189B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8777F13-A805-4C6B-87B3-1C927FB8B831}"/>
   </bookViews>
@@ -17,22 +17,11 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="36" r:id="rId2"/>
+    <pivotCache cacheId="0" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -227,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,14 +225,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -272,8 +253,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -306,6 +309,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,36 +395,25 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
@@ -432,15 +430,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -448,104 +437,166 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="4" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="7" borderId="1" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" pivotButton="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="40% - Accent2" xfId="2" builtinId="35"/>
-    <cellStyle name="40% - Accent3" xfId="3" builtinId="39"/>
-    <cellStyle name="40% - Accent5" xfId="4" builtinId="47"/>
+    <cellStyle name="40 % - Accent2" xfId="2" builtinId="35"/>
+    <cellStyle name="40 % - Accent3" xfId="3" builtinId="39"/>
+    <cellStyle name="40 % - Accent5" xfId="4" builtinId="47"/>
     <cellStyle name="Accent2" xfId="1" builtinId="33"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="14"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -582,17 +633,77 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="thin">
           <color auto="1"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -606,6 +717,13 @@
         <top style="thin">
           <color auto="1"/>
         </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
@@ -906,7 +1024,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13B4FA5D-0F92-4A69-949F-274980E58879}" name="PivotTable8" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{13B4FA5D-0F92-4A69-949F-274980E58879}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A47:B82" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -1074,6 +1192,92 @@
   <dataFields count="1">
     <dataField name="Sum of Temps estimé (minutes)" fld="3" baseField="0" baseItem="0" numFmtId="2"/>
   </dataFields>
+  <formats count="12">
+    <format dxfId="16">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="11">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="10">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -1087,14 +1291,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{FAC5B138-E55B-4D83-A16E-F11FEF647731}" name="todo" displayName="todo" ref="A15:E45" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{FAC5B138-E55B-4D83-A16E-F11FEF647731}" name="todo" displayName="todo" ref="A15:E45" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="26" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <autoFilter ref="A15:E45" xr:uid="{FAC5B138-E55B-4D83-A16E-F11FEF647731}"/>
   <tableColumns count="5">
-    <tableColumn id="2" xr3:uid="{0FA5E4A1-ED0A-436E-B50B-87E5FF195AF7}" name="Tâche" dataDxfId="3" dataCellStyle="40% - Accent3"/>
-    <tableColumn id="7" xr3:uid="{AEBC95C1-BC25-417B-98D8-A2A9347872A1}" name="Phase" dataDxfId="0" dataCellStyle="Accent2"/>
-    <tableColumn id="3" xr3:uid="{5D2A211B-9064-4A08-9543-ABB38C3A9FE3}" name="Responsable" dataDxfId="1" dataCellStyle="40% - Accent3"/>
-    <tableColumn id="4" xr3:uid="{3A09BFC1-6646-4E85-8B40-CDAB77E2C9AF}" name="Temps estimé (minutes)" dataDxfId="2" dataCellStyle="40% - Accent3"/>
-    <tableColumn id="5" xr3:uid="{976B5F55-9EF8-4F35-8FD1-BEF07761F2D7}" name="Statut" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{0FA5E4A1-ED0A-436E-B50B-87E5FF195AF7}" name="Tâche" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{AEBC95C1-BC25-417B-98D8-A2A9347872A1}" name="Phase" dataDxfId="22" dataCellStyle="Accent2"/>
+    <tableColumn id="3" xr3:uid="{5D2A211B-9064-4A08-9543-ABB38C3A9FE3}" name="Responsable" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{3A09BFC1-6646-4E85-8B40-CDAB77E2C9AF}" name="Temps estimé (minutes)" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{976B5F55-9EF8-4F35-8FD1-BEF07761F2D7}" name="Statut" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1417,987 +1621,920 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDABB652-F750-4B77-98E6-07E9B614649D}">
-  <dimension ref="A1:F95"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E82"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="93.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
-    <col min="5" max="5" width="21.88671875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" customWidth="1"/>
-    <col min="7" max="7" width="36.109375" customWidth="1"/>
+    <col min="1" max="1" width="93.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.8984375" customWidth="1"/>
+    <col min="3" max="3" width="36.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.296875" customWidth="1"/>
+    <col min="5" max="5" width="21.8984375" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" customWidth="1"/>
+    <col min="7" max="7" width="36.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" ht="28.2">
+      <c r="A1" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2"/>
-      <c r="D2" s="4"/>
-      <c r="E2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="B1" s="28"/>
+    </row>
+    <row r="3" spans="1:5" s="33" customFormat="1" ht="18">
+      <c r="A3" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="6"/>
-      <c r="E3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="B3" s="35"/>
+      <c r="C3" s="36"/>
+    </row>
+    <row r="4" spans="1:5" s="33" customFormat="1" ht="18">
+      <c r="A4" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="E4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="5">
         <v>2512</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="E5"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="4">
         <v>2634</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="E6"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="3">
         <v>2726</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="E7"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8"/>
-      <c r="D8" s="4"/>
-      <c r="E8"/>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="15.6" customHeight="1"/>
+    <row r="9" spans="1:5" s="33" customFormat="1" ht="15.6" customHeight="1">
+      <c r="A9" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="34"/>
-    </row>
-    <row r="10" spans="1:6" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="B9" s="38"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A10" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" s="4" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.6" customHeight="1">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" s="33" customFormat="1" ht="18">
+      <c r="A15" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="32" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:5">
+      <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="11">
         <v>1</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="9">
         <v>120</v>
       </c>
-      <c r="E16" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="E16" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="11">
         <v>1</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="9">
         <v>120</v>
       </c>
-      <c r="E17" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="E17" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="11">
         <v>1</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="9">
         <v>180</v>
       </c>
-      <c r="E18" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="E18" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="12">
         <v>1</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="8">
         <v>120</v>
       </c>
-      <c r="E19" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+      <c r="E19" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="12">
         <v>1</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="8">
         <v>120</v>
       </c>
-      <c r="E20" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+      <c r="E20" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="12">
         <v>1</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="8">
         <v>90</v>
       </c>
-      <c r="E21" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="E21" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="13">
         <v>1</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="10">
         <v>150</v>
       </c>
-      <c r="E22" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+      <c r="E22" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="13">
         <v>1</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="10">
         <v>180</v>
       </c>
-      <c r="E23" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+      <c r="E23" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="13">
         <v>1</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="10">
         <v>180</v>
       </c>
-      <c r="E24" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+      <c r="E24" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="11">
         <v>2</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="9">
         <v>120</v>
       </c>
-      <c r="E25" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="E25" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="11">
         <v>2</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="9">
         <v>120</v>
       </c>
-      <c r="E26" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+      <c r="E26" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="12">
         <v>2</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="8">
         <v>120</v>
       </c>
-      <c r="E27" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+      <c r="E27" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="19">
+      <c r="B28" s="12">
         <v>2</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="8">
         <v>120</v>
       </c>
-      <c r="E28" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
+      <c r="E28" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="11">
         <v>2</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="9">
         <v>90</v>
       </c>
-      <c r="E29" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+      <c r="E29" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="11">
         <v>2</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="9">
         <v>60</v>
       </c>
-      <c r="E30" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
+      <c r="E30" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="25">
         <v>2</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="27">
+        <v>180</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="13">
+        <v>2</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="10">
+        <v>180</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="11">
+        <v>2</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="9">
+        <v>30</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="11">
+        <v>2</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="9">
+        <v>30</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" s="11">
+        <v>2</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="9">
+        <v>90</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" s="13">
+        <v>2</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="10">
+        <v>90</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="13">
+        <v>2</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="10">
+        <v>90</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="11">
+        <v>2</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="9">
+        <v>60</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B39" s="11">
+        <v>2</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="9">
+        <v>30</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="12">
+        <v>2</v>
+      </c>
+      <c r="C40" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D40" s="8">
         <v>180</v>
       </c>
-      <c r="E31" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
+      <c r="E40" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" s="12">
+        <v>2</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="8">
+        <v>110</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" s="13">
+        <v>2</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="10">
+        <v>180</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B43" s="13">
+        <v>2</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="10">
+        <v>60</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="20">
+        <v>3</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="23">
+        <v>60</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="20">
+        <v>3</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="23">
+        <v>180</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" s="33" customFormat="1" ht="18">
+      <c r="A47" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" s="29" customFormat="1" ht="15.6">
+      <c r="A48" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="41">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" s="15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B58" s="15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" s="15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" s="29" customFormat="1" ht="15.6">
+      <c r="A61" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="41">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B64" s="15">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="15">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" s="15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" s="15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" s="29" customFormat="1" ht="15.6">
+      <c r="A70" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" s="41">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" s="15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B72" s="15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="20">
-        <v>2</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="17">
+      <c r="B73" s="15">
         <v>180</v>
       </c>
-      <c r="E32" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="18">
-        <v>2</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="16">
-        <v>30</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="18">
-        <v>2</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="16">
-        <v>30</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="18">
-        <v>2</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="16">
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" s="15">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B75" s="15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" s="15">
         <v>90</v>
       </c>
-      <c r="E35" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="20">
-        <v>2</v>
-      </c>
-      <c r="C36" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="17">
+      <c r="B77" s="15">
         <v>90</v>
       </c>
-      <c r="E36" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" s="20">
-        <v>2</v>
-      </c>
-      <c r="C37" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" s="17">
-        <v>90</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B38" s="18">
-        <v>2</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="16">
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" s="29" customFormat="1" ht="15.6">
+      <c r="A79" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" s="41">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B80" s="15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" s="15">
         <v>60</v>
       </c>
-      <c r="E38" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B39" s="18">
-        <v>2</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="16">
-        <v>30</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="19">
-        <v>2</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="15">
-        <v>180</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B41" s="19">
-        <v>2</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="15">
-        <v>110</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="20">
-        <v>2</v>
-      </c>
-      <c r="C42" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D42" s="17">
-        <v>180</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43" s="20">
-        <v>2</v>
-      </c>
-      <c r="C43" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D43" s="17">
-        <v>60</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="30">
-        <v>3</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="D44" s="33">
-        <v>60</v>
-      </c>
-      <c r="E44" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" s="30">
-        <v>3</v>
-      </c>
-      <c r="C45" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="33">
-        <v>180</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="25">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" s="25">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" s="25">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B51" s="25">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="25">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" s="25">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="B54" s="25">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="25">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B56" s="25">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B57" s="25">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B58" s="25">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B59" s="25">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B60" s="25">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="25">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B62" s="25">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B63" s="25">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B64" s="25">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B65" s="25">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="25">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B67" s="25">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B68" s="25">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B69" s="25">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="25">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" s="25">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B72" s="25">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B73" s="25">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B74" s="25">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B75" s="25">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B76" s="25">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B77" s="25">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="25">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="25">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B80" s="25">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B81" s="25">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="5" t="s">
+    </row>
+    <row r="82" spans="1:2" s="33" customFormat="1" ht="18">
+      <c r="A82" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="B82" s="25">
+      <c r="B82" s="43">
         <v>3440</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93"/>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94"/>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95"/>
     </row>
   </sheetData>
   <mergeCells count="2">
